--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/01. Báo giá sửa chữa/BG_AnhTuanNB_011026.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/01. Báo giá sửa chữa/BG_AnhTuanNB_011026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 10\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4343B7-9569-4595-9490-DFC10359B041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5A01EA-4C37-400E-A190-71EF00D97801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="BG" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$24</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -146,7 +146,25 @@
     <t>SIM lúc nhận lúc không (phản hồi từ khách)</t>
   </si>
   <si>
-    <t>Hà Nội, ngày 01 tháng 09 năm 2026</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>TG102LE-4G</t>
+  </si>
+  <si>
+    <t>005694061436858</t>
+  </si>
+  <si>
+    <t>Thường xuyên mất GPS</t>
+  </si>
+  <si>
+    <t>Module GPS</t>
+  </si>
+  <si>
+    <t>110,000</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày 01 tháng 10 năm 2026</t>
   </si>
 </sst>
 </file>
@@ -515,6 +533,69 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -531,69 +612,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -955,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
@@ -977,74 +995,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43"/>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="49" t="s">
+      <c r="A1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="51"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="52" t="s">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="54"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="48"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="55" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="57"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="58" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="42"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="36"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -1059,7 +1077,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="29" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -1207,7 +1225,7 @@
         <v>32</v>
       </c>
       <c r="J12" s="17">
-        <f t="shared" ref="J12:J14" si="0">SUM(H12*I12)</f>
+        <f t="shared" ref="J12:J15" si="0">SUM(H12*I12)</f>
         <v>130000</v>
       </c>
       <c r="K12" s="22"/>
@@ -1280,97 +1298,117 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="33">
-        <f>SUM(J11:J14)</f>
-        <v>520000</v>
+      <c r="A15" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="17">
+        <f t="shared" si="0"/>
+        <v>110000</v>
       </c>
       <c r="K15" s="22"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="13"/>
+      <c r="A16" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="33">
+        <f>SUM(J11:J15)</f>
+        <v>630000</v>
+      </c>
+      <c r="K16" s="22"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="13"/>
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37" t="s">
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="AA17" s="2"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="AA18" s="2"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38" t="s">
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="AA18" s="2"/>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
@@ -1379,7 +1417,9 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>1</v>
+      </c>
       <c r="G21" s="11"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
@@ -1400,28 +1440,38 @@
       <c r="AA22" s="2"/>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="AA23" s="2"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A24" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39" t="s">
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="8"/>
-      <c r="AA23" s="2"/>
-    </row>
-    <row r="24" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="F24" s="4"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="8"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F25" s="4"/>
       <c r="AA25" s="2"/>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
@@ -1474,23 +1524,26 @@
     </row>
     <row r="42" spans="27:27" x14ac:dyDescent="0.25">
       <c r="AA42" s="2"/>
+    </row>
+    <row r="43" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA43" s="2"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="13">
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="F24:J24"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A1:D4"/>
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="E2:J2"/>
     <mergeCell ref="E3:J3"/>
     <mergeCell ref="E4:J4"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="F23:J23"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/01. Báo giá sửa chữa/BG_AnhTuanNB_011026.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/01. Báo giá sửa chữa/BG_AnhTuanNB_011026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 10\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5A01EA-4C37-400E-A190-71EF00D97801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2521CA85-283D-43C1-BAC7-1DA907D7093E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>Hà Nội, ngày 01 tháng 10 năm 2026</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Báo giá khách đã đồng ý, công nợ ghi KD</t>
   </si>
 </sst>
 </file>
@@ -533,6 +539,24 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -594,24 +618,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -995,74 +1001,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="43" t="s">
+      <c r="A1" s="43"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="45"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="37"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="46" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="48"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="54"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="37"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="49" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="51"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="52" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="54"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="42"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -1158,7 +1164,9 @@
       <c r="J10" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="22"/>
+      <c r="K10" s="22" t="s">
+        <v>47</v>
+      </c>
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -1193,7 +1201,9 @@
         <f>SUM(H11*I11)</f>
         <v>130000</v>
       </c>
-      <c r="K11" s="22"/>
+      <c r="K11" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -1333,17 +1343,17 @@
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="57"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="36"/>
       <c r="J16" s="33">
         <f>SUM(J11:J15)</f>
         <v>630000</v>
@@ -1365,37 +1375,37 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="58" t="s">
+      <c r="A18" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58" t="s">
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59" t="s">
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
@@ -1453,20 +1463,20 @@
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="60"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60" t="s">
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="60"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
       <c r="K24" s="8"/>
       <c r="AA24" s="2"/>
     </row>
@@ -1531,6 +1541,12 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="13">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
@@ -1538,12 +1554,6 @@
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="F24:J24"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/01. Báo giá sửa chữa/BG_AnhTuanNB_011026.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/01. Báo giá sửa chữa/BG_AnhTuanNB_011026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 10\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2521CA85-283D-43C1-BAC7-1DA907D7093E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F2BA10-CEF3-4FA8-A179-8D749E331E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -171,13 +171,19 @@
   </si>
   <si>
     <t>Báo giá khách đã đồng ý, công nợ ghi KD</t>
+  </si>
+  <si>
+    <t>Còn BH</t>
+  </si>
+  <si>
+    <t>Huỷ báo mã này kiểm tra nhầm ngày bán( thiết bị còn BH)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,8 +276,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,6 +299,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -539,6 +563,69 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -557,67 +644,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1001,74 +1042,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43"/>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="49" t="s">
+      <c r="A1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="51"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="52" t="s">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="54"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="48"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="55" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="57"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="58" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="42"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="36"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -1241,38 +1282,40 @@
       <c r="K12" s="22"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+    <row r="13" spans="1:27" s="62" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31" t="s">
+      <c r="D13" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="64"/>
+      <c r="F13" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="67">
         <f t="shared" si="0"/>
         <v>130000</v>
       </c>
-      <c r="K13" s="22"/>
-      <c r="AA13" s="2"/>
+      <c r="K13" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA13" s="63"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
@@ -1343,17 +1386,17 @@
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="57"/>
       <c r="J16" s="33">
         <f>SUM(J11:J15)</f>
         <v>630000</v>
@@ -1375,37 +1418,37 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37" t="s">
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38" t="s">
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
@@ -1463,20 +1506,20 @@
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39" t="s">
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="60"/>
       <c r="K24" s="8"/>
       <c r="AA24" s="2"/>
     </row>
@@ -1541,12 +1584,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="13">
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
@@ -1554,6 +1591,12 @@
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="F24:J24"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
